--- a/Datos Experimentales/Data 24031.xlsx
+++ b/Datos Experimentales/Data 24031.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67AA757-E2CE-4E22-957C-EF8DF6248079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Antecedentes_info" sheetId="1" r:id="rId1"/>
     <sheet name="Antecedentes" sheetId="2" r:id="rId2"/>
@@ -18,6 +28,7 @@
     <sheet name="Manual Densidades" sheetId="13" r:id="rId13"/>
     <sheet name="Winegrid densidad" sheetId="14" r:id="rId14"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -960,11 +971,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -993,14 +1001,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1325,10 +1342,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B108"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1336,7 +1354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1344,7 +1362,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1352,7 +1370,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1360,7 +1378,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1368,7 +1386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1376,7 +1394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1384,7 +1402,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1392,7 +1410,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1400,7 +1418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1408,7 +1426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1416,7 +1434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1424,7 +1442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1432,7 +1450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1440,7 +1458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1448,7 +1466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1456,7 +1474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1464,7 +1482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1472,7 +1490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1480,7 +1498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1488,7 +1506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1496,7 +1514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1504,7 +1522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1512,7 +1530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1520,7 +1538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1528,7 +1546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1536,7 +1554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1544,7 +1562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1552,7 +1570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1560,7 +1578,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1568,7 +1586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1576,7 +1594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1584,7 +1602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1592,7 +1610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1600,7 +1618,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1608,7 +1626,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1616,7 +1634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1624,7 +1642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1632,7 +1650,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1640,7 +1658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1648,7 +1666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1656,7 +1674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1664,7 +1682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1672,7 +1690,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1680,7 +1698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1688,7 +1706,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1696,7 +1714,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1704,7 +1722,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1712,7 +1730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1720,7 +1738,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1728,7 +1746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1736,7 +1754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1744,7 +1762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1752,7 +1770,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1760,7 +1778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1768,7 +1786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1776,7 +1794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1784,7 +1802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1792,7 +1810,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1800,7 +1818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1808,7 +1826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1816,7 +1834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1824,7 +1842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1832,7 +1850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1840,7 +1858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1848,7 +1866,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1856,7 +1874,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -1864,7 +1882,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -1872,7 +1890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -1880,7 +1898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -1888,7 +1906,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -1896,7 +1914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>82</v>
       </c>
@@ -1904,7 +1922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -1912,7 +1930,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -1920,7 +1938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>86</v>
       </c>
@@ -1928,7 +1946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -1936,7 +1954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -1944,7 +1962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>89</v>
       </c>
@@ -1952,7 +1970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -1960,7 +1978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>91</v>
       </c>
@@ -1968,7 +1986,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -1976,7 +1994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>93</v>
       </c>
@@ -1984,7 +2002,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -1992,7 +2010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2000,7 +2018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2008,7 +2026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2016,7 +2034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -2024,7 +2042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -2032,7 +2050,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>101</v>
       </c>
@@ -2040,7 +2058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>102</v>
       </c>
@@ -2048,7 +2066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>103</v>
       </c>
@@ -2056,7 +2074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>104</v>
       </c>
@@ -2064,7 +2082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>105</v>
       </c>
@@ -2072,7 +2090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>106</v>
       </c>
@@ -2080,7 +2098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>107</v>
       </c>
@@ -2088,7 +2106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>108</v>
       </c>
@@ -2096,7 +2114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>109</v>
       </c>
@@ -2104,7 +2122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2112,7 +2130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2120,7 +2138,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2128,7 +2146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2136,7 +2154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -2144,7 +2162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2152,7 +2170,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>117</v>
       </c>
@@ -2160,7 +2178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>118</v>
       </c>
@@ -2168,7 +2186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>119</v>
       </c>
@@ -2176,7 +2194,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>120</v>
       </c>
@@ -2184,7 +2202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>121</v>
       </c>
@@ -2193,27 +2211,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B108"/>
+    <ignoredError sqref="A1:B108" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>272</v>
       </c>
@@ -2234,17 +2256,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>277</v>
       </c>
@@ -2255,7 +2279,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>280</v>
       </c>
@@ -2266,7 +2290,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>281</v>
       </c>
@@ -2277,29 +2301,29 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>282</v>
       </c>
       <c r="B4">
-        <v>0.7194444444444444</v>
+        <v>0.71944444444444444</v>
       </c>
       <c r="C4">
         <v>19.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>283</v>
       </c>
       <c r="B5">
-        <v>0.9694444444444444</v>
+        <v>0.96944444444444444</v>
       </c>
       <c r="C5">
         <v>20</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>284</v>
       </c>
@@ -2310,7 +2334,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>285</v>
       </c>
@@ -2321,7 +2345,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>286</v>
       </c>
@@ -2332,7 +2356,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>287</v>
       </c>
@@ -2343,7 +2367,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>288</v>
       </c>
@@ -2354,7 +2378,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>289</v>
       </c>
@@ -2365,7 +2389,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>290</v>
       </c>
@@ -2373,10 +2397,10 @@
         <v>2.7194444444444446</v>
       </c>
       <c r="C12">
-        <v>19.6</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>291</v>
       </c>
@@ -2387,7 +2411,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>292</v>
       </c>
@@ -2395,10 +2419,10 @@
         <v>3.2194444444444446</v>
       </c>
       <c r="C14">
-        <v>19.6</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>293</v>
       </c>
@@ -2409,7 +2433,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>294</v>
       </c>
@@ -2420,7 +2444,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>295</v>
       </c>
@@ -2431,150 +2455,152 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>296</v>
       </c>
       <c r="B18">
-        <v>4.219444444444444</v>
+        <v>4.2194444444444441</v>
       </c>
       <c r="C18">
         <v>19.5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>297</v>
       </c>
       <c r="B19">
-        <v>4.469444444444444</v>
+        <v>4.4694444444444441</v>
       </c>
       <c r="C19">
         <v>20.8</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>298</v>
       </c>
       <c r="B20">
-        <v>4.719444444444444</v>
+        <v>4.7194444444444441</v>
       </c>
       <c r="C20">
         <v>20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>299</v>
       </c>
       <c r="B21">
-        <v>4.969444444444444</v>
+        <v>4.9694444444444441</v>
       </c>
       <c r="C21">
         <v>21</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>300</v>
       </c>
       <c r="B22">
-        <v>5.219444444444444</v>
+        <v>5.2194444444444441</v>
       </c>
       <c r="C22">
         <v>20</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>301</v>
       </c>
       <c r="B23">
-        <v>5.469444444444444</v>
+        <v>5.4694444444444441</v>
       </c>
       <c r="C23">
-        <v>19.4</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>302</v>
       </c>
       <c r="B24">
-        <v>5.719444444444444</v>
+        <v>5.7194444444444441</v>
       </c>
       <c r="C24">
         <v>20</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>303</v>
       </c>
       <c r="B25">
-        <v>5.969444444444444</v>
+        <v>5.9694444444444441</v>
       </c>
       <c r="C25">
         <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>304</v>
       </c>
       <c r="B26">
-        <v>6.219444444444444</v>
+        <v>6.2194444444444441</v>
       </c>
       <c r="C26">
         <v>19.2</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>305</v>
       </c>
       <c r="B27">
-        <v>6.469444444444444</v>
+        <v>6.4694444444444441</v>
       </c>
       <c r="C27">
         <v>21.3</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>306</v>
       </c>
       <c r="B28">
-        <v>6.719444444444444</v>
+        <v>6.7194444444444441</v>
       </c>
       <c r="C28">
         <v>20</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>307</v>
       </c>
       <c r="B29">
-        <v>6.969444444444444</v>
+        <v>6.9694444444444441</v>
       </c>
       <c r="C29">
         <v>20</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C29"/>
+    <ignoredError sqref="A1:C29" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>277</v>
       </c>
@@ -2585,7 +2611,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>280</v>
       </c>
@@ -2596,7 +2622,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>281</v>
       </c>
@@ -2607,29 +2633,29 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>282</v>
       </c>
       <c r="B4">
-        <v>0.7194444444444444</v>
+        <v>0.71944444444444444</v>
       </c>
       <c r="C4">
         <v>1079</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>283</v>
       </c>
       <c r="B5">
-        <v>0.9694444444444444</v>
+        <v>0.96944444444444444</v>
       </c>
       <c r="C5">
         <v>1072</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>284</v>
       </c>
@@ -2640,7 +2666,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>285</v>
       </c>
@@ -2651,7 +2677,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>286</v>
       </c>
@@ -2662,7 +2688,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>287</v>
       </c>
@@ -2673,7 +2699,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>288</v>
       </c>
@@ -2684,7 +2710,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>289</v>
       </c>
@@ -2695,7 +2721,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>290</v>
       </c>
@@ -2706,7 +2732,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>291</v>
       </c>
@@ -2717,7 +2743,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>292</v>
       </c>
@@ -2728,7 +2754,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>293</v>
       </c>
@@ -2739,7 +2765,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>294</v>
       </c>
@@ -2750,7 +2776,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>295</v>
       </c>
@@ -2761,150 +2787,152 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>296</v>
       </c>
       <c r="B18">
-        <v>4.219444444444444</v>
+        <v>4.2194444444444441</v>
       </c>
       <c r="C18">
         <v>1006</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>297</v>
       </c>
       <c r="B19">
-        <v>4.469444444444444</v>
+        <v>4.4694444444444441</v>
       </c>
       <c r="C19">
         <v>1004</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>298</v>
       </c>
       <c r="B20">
-        <v>4.719444444444444</v>
+        <v>4.7194444444444441</v>
       </c>
       <c r="C20">
         <v>1001</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>299</v>
       </c>
       <c r="B21">
-        <v>4.969444444444444</v>
+        <v>4.9694444444444441</v>
       </c>
       <c r="C21">
         <v>999</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>300</v>
       </c>
       <c r="B22">
-        <v>5.219444444444444</v>
+        <v>5.2194444444444441</v>
       </c>
       <c r="C22">
         <v>998</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>301</v>
       </c>
       <c r="B23">
-        <v>5.469444444444444</v>
+        <v>5.4694444444444441</v>
       </c>
       <c r="C23">
         <v>997</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>302</v>
       </c>
       <c r="B24">
-        <v>5.719444444444444</v>
+        <v>5.7194444444444441</v>
       </c>
       <c r="C24">
         <v>997</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>303</v>
       </c>
       <c r="B25">
-        <v>5.969444444444444</v>
+        <v>5.9694444444444441</v>
       </c>
       <c r="C25">
         <v>996</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>304</v>
       </c>
       <c r="B26">
-        <v>6.219444444444444</v>
+        <v>6.2194444444444441</v>
       </c>
       <c r="C26">
         <v>996</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>305</v>
       </c>
       <c r="B27">
-        <v>6.469444444444444</v>
+        <v>6.4694444444444441</v>
       </c>
       <c r="C27">
         <v>995</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>306</v>
       </c>
       <c r="B28">
-        <v>6.719444444444444</v>
+        <v>6.7194444444444441</v>
       </c>
       <c r="C28">
         <v>994</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>307</v>
       </c>
       <c r="B29">
-        <v>6.969444444444444</v>
+        <v>6.9694444444444441</v>
       </c>
       <c r="C29">
         <v>994</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C29"/>
+    <ignoredError sqref="A1:C29" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>277</v>
       </c>
@@ -2928,17 +2956,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CQ2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:95" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3225,7 +3255,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:95" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9850</v>
       </c>
@@ -3260,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>45373.65555555555</v>
+        <v>45373.655555555553</v>
       </c>
       <c r="M2" t="s">
         <v>126</v>
@@ -3269,7 +3299,7 @@
         <v>127</v>
       </c>
       <c r="O2">
-        <v>45380.65555555555</v>
+        <v>45380.655555555553</v>
       </c>
       <c r="P2" t="s">
         <v>128</v>
@@ -3422,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="BQ2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="BR2">
         <v>0</v>
@@ -3464,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="CE2">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="CF2">
         <v>0</v>
@@ -3492,17 +3522,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CQ2"/>
+    <ignoredError sqref="A1:CQ2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -3555,7 +3587,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9850</v>
       </c>
@@ -3584,7 +3616,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9850</v>
       </c>
@@ -3619,7 +3651,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9850</v>
       </c>
@@ -3648,7 +3680,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9850</v>
       </c>
@@ -3662,7 +3694,7 @@
         <v>170</v>
       </c>
       <c r="E5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="F5" t="s">
         <v>166</v>
@@ -3698,7 +3730,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9850</v>
       </c>
@@ -3712,7 +3744,7 @@
         <v>170</v>
       </c>
       <c r="E6">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="F6" t="s">
         <v>166</v>
@@ -3748,7 +3780,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9850</v>
       </c>
@@ -3783,7 +3815,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9850</v>
       </c>
@@ -3830,7 +3862,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9850</v>
       </c>
@@ -3859,7 +3891,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9850</v>
       </c>
@@ -3894,7 +3926,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9850</v>
       </c>
@@ -3929,7 +3961,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9850</v>
       </c>
@@ -3965,17 +3997,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError sqref="A1:Q12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -4007,7 +4041,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9850</v>
       </c>
@@ -4039,7 +4073,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9850</v>
       </c>
@@ -4071,7 +4105,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9850</v>
       </c>
@@ -4104,27 +4138,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError sqref="A1:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -4156,7 +4194,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9850</v>
       </c>
@@ -4189,17 +4227,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError sqref="A1:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -4216,7 +4256,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9850</v>
       </c>
@@ -4228,27 +4268,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError sqref="A1:E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -4298,7 +4342,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9850</v>
       </c>
@@ -4311,7 +4355,7 @@
       <c r="D2">
         <v>6825</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>45373.781053240746</v>
       </c>
       <c r="F2" t="s">
@@ -4342,13 +4386,13 @@
         <v>228</v>
       </c>
       <c r="O2">
-        <v>7.5735</v>
+        <v>7.5735000000000001</v>
       </c>
       <c r="P2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9850</v>
       </c>
@@ -4361,7 +4405,7 @@
       <c r="D3">
         <v>6825</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>45373.781053240746</v>
       </c>
       <c r="F3" t="s">
@@ -4392,13 +4436,13 @@
         <v>228</v>
       </c>
       <c r="O3">
-        <v>3.435</v>
+        <v>3.4350000000000001</v>
       </c>
       <c r="P3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9850</v>
       </c>
@@ -4411,7 +4455,7 @@
       <c r="D4">
         <v>6825</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>45373.781053240746</v>
       </c>
       <c r="F4" t="s">
@@ -4448,7 +4492,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9850</v>
       </c>
@@ -4461,7 +4505,7 @@
       <c r="D5">
         <v>6825</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>45373.781053240746</v>
       </c>
       <c r="F5" t="s">
@@ -4498,7 +4542,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9850</v>
       </c>
@@ -4511,7 +4555,7 @@
       <c r="D6">
         <v>6825</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>45373.781053240746</v>
       </c>
       <c r="F6" t="s">
@@ -4548,7 +4592,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9850</v>
       </c>
@@ -4561,7 +4605,7 @@
       <c r="D7">
         <v>6825</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>45373.781053240746</v>
       </c>
       <c r="F7" t="s">
@@ -4598,7 +4642,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9850</v>
       </c>
@@ -4611,7 +4655,7 @@
       <c r="D8">
         <v>6825</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>45373.781053240746</v>
       </c>
       <c r="F8" t="s">
@@ -4648,7 +4692,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9850</v>
       </c>
@@ -4661,8 +4705,8 @@
       <c r="D9">
         <v>6892</v>
       </c>
-      <c r="E9">
-        <v>45376.660046296296</v>
+      <c r="E9" s="1">
+        <v>45373.660046296296</v>
       </c>
       <c r="F9" t="s">
         <v>125</v>
@@ -4698,7 +4742,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9850</v>
       </c>
@@ -4711,8 +4755,8 @@
       <c r="D10">
         <v>6892</v>
       </c>
-      <c r="E10">
-        <v>45376.660046296296</v>
+      <c r="E10" s="1">
+        <v>45373.660046296296</v>
       </c>
       <c r="F10" t="s">
         <v>125</v>
@@ -4748,7 +4792,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9850</v>
       </c>
@@ -4761,8 +4805,8 @@
       <c r="D11">
         <v>6892</v>
       </c>
-      <c r="E11">
-        <v>45376.660046296296</v>
+      <c r="E11" s="1">
+        <v>45373.660046296296</v>
       </c>
       <c r="F11" t="s">
         <v>125</v>
@@ -4798,7 +4842,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9850</v>
       </c>
@@ -4811,8 +4855,8 @@
       <c r="D12">
         <v>6892</v>
       </c>
-      <c r="E12">
-        <v>45376.660046296296</v>
+      <c r="E12" s="1">
+        <v>45373.660046296296</v>
       </c>
       <c r="F12" t="s">
         <v>125</v>
@@ -4848,7 +4892,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9850</v>
       </c>
@@ -4861,8 +4905,8 @@
       <c r="D13">
         <v>6892</v>
       </c>
-      <c r="E13">
-        <v>45376.660046296296</v>
+      <c r="E13" s="1">
+        <v>45373.660046296296</v>
       </c>
       <c r="F13" t="s">
         <v>125</v>
@@ -4898,7 +4942,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9850</v>
       </c>
@@ -4911,8 +4955,8 @@
       <c r="D14">
         <v>6892</v>
       </c>
-      <c r="E14">
-        <v>45376.660046296296</v>
+      <c r="E14" s="1">
+        <v>45373.660046296296</v>
       </c>
       <c r="F14" t="s">
         <v>125</v>
@@ -4948,7 +4992,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9850</v>
       </c>
@@ -4961,8 +5005,8 @@
       <c r="D15">
         <v>6892</v>
       </c>
-      <c r="E15">
-        <v>45376.660046296296</v>
+      <c r="E15" s="1">
+        <v>45373.660046296296</v>
       </c>
       <c r="F15" t="s">
         <v>125</v>
@@ -4998,7 +5042,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9850</v>
       </c>
@@ -5011,7 +5055,7 @@
       <c r="D16">
         <v>7034</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>45379.860497685186</v>
       </c>
       <c r="F16" t="s">
@@ -5048,7 +5092,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9850</v>
       </c>
@@ -5061,8 +5105,8 @@
       <c r="D17">
         <v>7092</v>
       </c>
-      <c r="E17">
-        <v>45383.61644675926</v>
+      <c r="E17" s="1">
+        <v>45383.616446759261</v>
       </c>
       <c r="F17" t="s">
         <v>125</v>
@@ -5098,7 +5142,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9850</v>
       </c>
@@ -5111,7 +5155,7 @@
       <c r="D18">
         <v>7177</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>45384.867893518516</v>
       </c>
       <c r="F18" t="s">
@@ -5148,7 +5192,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9850</v>
       </c>
@@ -5161,7 +5205,7 @@
       <c r="D19">
         <v>7177</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>45384.867893518516</v>
       </c>
       <c r="F19" t="s">
@@ -5198,7 +5242,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9850</v>
       </c>
@@ -5211,7 +5255,7 @@
       <c r="D20">
         <v>7177</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>45384.867893518516</v>
       </c>
       <c r="F20" t="s">
@@ -5248,7 +5292,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9850</v>
       </c>
@@ -5261,7 +5305,7 @@
       <c r="D21">
         <v>7177</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>45384.867893518516</v>
       </c>
       <c r="F21" t="s">
@@ -5298,7 +5342,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9850</v>
       </c>
@@ -5311,7 +5355,7 @@
       <c r="D22">
         <v>7177</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>45384.867893518516</v>
       </c>
       <c r="F22" t="s">
@@ -5342,13 +5386,13 @@
         <v>228</v>
       </c>
       <c r="O22">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="P22" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9850</v>
       </c>
@@ -5361,7 +5405,7 @@
       <c r="D23">
         <v>7177</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>45384.867893518516</v>
       </c>
       <c r="F23" t="s">
@@ -5392,13 +5436,13 @@
         <v>228</v>
       </c>
       <c r="O23">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="P23" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9850</v>
       </c>
@@ -5411,7 +5455,7 @@
       <c r="D24">
         <v>7177</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>45384.867893518516</v>
       </c>
       <c r="F24" t="s">
@@ -5448,7 +5492,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9850</v>
       </c>
@@ -5461,7 +5505,7 @@
       <c r="D25">
         <v>7177</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>45384.867893518516</v>
       </c>
       <c r="F25" t="s">
@@ -5498,7 +5542,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9850</v>
       </c>
@@ -5511,7 +5555,7 @@
       <c r="D26">
         <v>7177</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>45384.867893518516</v>
       </c>
       <c r="F26" t="s">
@@ -5548,7 +5592,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9850</v>
       </c>
@@ -5561,8 +5605,8 @@
       <c r="D27">
         <v>7289</v>
       </c>
-      <c r="E27">
-        <v>45387.75334490741</v>
+      <c r="E27" s="1">
+        <v>45387.753344907411</v>
       </c>
       <c r="F27" t="s">
         <v>125</v>
@@ -5592,13 +5636,13 @@
         <v>228</v>
       </c>
       <c r="O27">
-        <v>4.98</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="P27" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9850</v>
       </c>
@@ -5611,8 +5655,8 @@
       <c r="D28">
         <v>7289</v>
       </c>
-      <c r="E28">
-        <v>45387.75334490741</v>
+      <c r="E28" s="1">
+        <v>45387.753344907411</v>
       </c>
       <c r="F28" t="s">
         <v>125</v>
@@ -5648,7 +5692,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9850</v>
       </c>
@@ -5661,8 +5705,8 @@
       <c r="D29">
         <v>7289</v>
       </c>
-      <c r="E29">
-        <v>45387.75334490741</v>
+      <c r="E29" s="1">
+        <v>45387.753344907411</v>
       </c>
       <c r="F29" t="s">
         <v>125</v>
@@ -5698,7 +5742,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9850</v>
       </c>
@@ -5711,8 +5755,8 @@
       <c r="D30">
         <v>7289</v>
       </c>
-      <c r="E30">
-        <v>45387.75334490741</v>
+      <c r="E30" s="1">
+        <v>45387.753344907411</v>
       </c>
       <c r="F30" t="s">
         <v>125</v>
@@ -5748,7 +5792,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9850</v>
       </c>
@@ -5761,8 +5805,8 @@
       <c r="D31">
         <v>7289</v>
       </c>
-      <c r="E31">
-        <v>45387.75334490741</v>
+      <c r="E31" s="1">
+        <v>45387.753344907411</v>
       </c>
       <c r="F31" t="s">
         <v>125</v>
@@ -5792,13 +5836,13 @@
         <v>228</v>
       </c>
       <c r="O31">
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="P31" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9850</v>
       </c>
@@ -5811,8 +5855,8 @@
       <c r="D32">
         <v>7289</v>
       </c>
-      <c r="E32">
-        <v>45387.75334490741</v>
+      <c r="E32" s="1">
+        <v>45387.753344907411</v>
       </c>
       <c r="F32" t="s">
         <v>125</v>
@@ -5848,7 +5892,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9850</v>
       </c>
@@ -5861,8 +5905,8 @@
       <c r="D33">
         <v>7289</v>
       </c>
-      <c r="E33">
-        <v>45387.75334490741</v>
+      <c r="E33" s="1">
+        <v>45387.753344907411</v>
       </c>
       <c r="F33" t="s">
         <v>125</v>
@@ -5892,13 +5936,13 @@
         <v>228</v>
       </c>
       <c r="O33">
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="P33" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9850</v>
       </c>
@@ -5911,8 +5955,8 @@
       <c r="D34">
         <v>7289</v>
       </c>
-      <c r="E34">
-        <v>45387.75334490741</v>
+      <c r="E34" s="1">
+        <v>45387.753344907411</v>
       </c>
       <c r="F34" t="s">
         <v>125</v>
@@ -5948,7 +5992,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9850</v>
       </c>
@@ -5961,8 +6005,8 @@
       <c r="D35">
         <v>7289</v>
       </c>
-      <c r="E35">
-        <v>45387.75334490741</v>
+      <c r="E35" s="1">
+        <v>45387.753344907411</v>
       </c>
       <c r="F35" t="s">
         <v>125</v>
@@ -5998,7 +6042,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9850</v>
       </c>
@@ -6011,8 +6055,8 @@
       <c r="D36">
         <v>7289</v>
       </c>
-      <c r="E36">
-        <v>45387.75334490741</v>
+      <c r="E36" s="1">
+        <v>45387.753344907411</v>
       </c>
       <c r="F36" t="s">
         <v>125</v>
@@ -6049,8 +6093,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P36"/>
+    <ignoredError sqref="A1:P8 A16:P36 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Datos Experimentales/Data 24031.xlsx
+++ b/Datos Experimentales/Data 24031.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67AA757-E2CE-4E22-957C-EF8DF6248079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC8BA2F-3A4C-4DDA-9706-28400FFB6EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -972,8 +972,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1001,9 +1009,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1344,9 +1353,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B108"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1354,7 +1363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1362,7 +1371,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1370,7 +1379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1378,7 +1387,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1386,7 +1395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1394,7 +1403,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1402,7 +1411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1410,7 +1419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1418,7 +1427,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1426,7 +1435,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1434,7 +1443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1442,7 +1451,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1450,7 +1459,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1458,7 +1467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1466,7 +1475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1474,7 +1483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1482,7 +1491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1490,7 +1499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1498,7 +1507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1506,7 +1515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1514,7 +1523,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1522,7 +1531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1530,7 +1539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1538,7 +1547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1546,7 +1555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1554,7 +1563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1562,7 +1571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1570,7 +1579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1578,7 +1587,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1586,7 +1595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1594,7 +1603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1602,7 +1611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1610,7 +1619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1618,7 +1627,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1626,7 +1635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1634,7 +1643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1642,7 +1651,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1650,7 +1659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1658,7 +1667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1666,7 +1675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1674,7 +1683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1682,7 +1691,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1690,7 +1699,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1698,7 +1707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1706,7 +1715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1714,7 +1723,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1722,7 +1731,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1730,7 +1739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1738,7 +1747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1746,7 +1755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1754,7 +1763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1762,7 +1771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1770,7 +1779,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1778,7 +1787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1786,7 +1795,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1794,7 +1803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1802,7 +1811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1810,7 +1819,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1818,7 +1827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1826,7 +1835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1834,7 +1843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1842,7 +1851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1850,7 +1859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1858,7 +1867,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1866,7 +1875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1874,7 +1883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -1882,7 +1891,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -1890,7 +1899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -1898,7 +1907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -1906,7 +1915,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -1914,7 +1923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>82</v>
       </c>
@@ -1922,7 +1931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -1930,7 +1939,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -1938,7 +1947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>86</v>
       </c>
@@ -1946,7 +1955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -1954,7 +1963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -1962,7 +1971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>89</v>
       </c>
@@ -1970,7 +1979,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -1978,7 +1987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>91</v>
       </c>
@@ -1986,7 +1995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -1994,7 +2003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>93</v>
       </c>
@@ -2002,7 +2011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -2010,7 +2019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2018,7 +2027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2026,7 +2035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2034,7 +2043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -2042,7 +2051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -2050,7 +2059,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>101</v>
       </c>
@@ -2058,7 +2067,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>102</v>
       </c>
@@ -2066,7 +2075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>103</v>
       </c>
@@ -2074,7 +2083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>104</v>
       </c>
@@ -2082,7 +2091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>105</v>
       </c>
@@ -2090,7 +2099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>106</v>
       </c>
@@ -2098,7 +2107,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>107</v>
       </c>
@@ -2106,7 +2115,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>108</v>
       </c>
@@ -2114,7 +2123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>109</v>
       </c>
@@ -2122,7 +2131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2130,7 +2139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2138,7 +2147,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2146,7 +2155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2154,7 +2163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -2162,7 +2171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2170,7 +2179,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>117</v>
       </c>
@@ -2178,7 +2187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>118</v>
       </c>
@@ -2186,7 +2195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>119</v>
       </c>
@@ -2194,7 +2203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>120</v>
       </c>
@@ -2202,7 +2211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>121</v>
       </c>
@@ -2221,7 +2230,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -2233,9 +2242,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>272</v>
       </c>
@@ -2266,9 +2275,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>277</v>
       </c>
@@ -2279,7 +2288,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>280</v>
       </c>
@@ -2290,7 +2299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>281</v>
       </c>
@@ -2301,7 +2310,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>282</v>
       </c>
@@ -2312,7 +2321,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>283</v>
       </c>
@@ -2323,7 +2332,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>284</v>
       </c>
@@ -2334,7 +2343,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>285</v>
       </c>
@@ -2345,7 +2354,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>286</v>
       </c>
@@ -2356,7 +2365,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>287</v>
       </c>
@@ -2367,7 +2376,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>288</v>
       </c>
@@ -2378,7 +2387,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>289</v>
       </c>
@@ -2389,7 +2398,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>290</v>
       </c>
@@ -2400,7 +2409,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>291</v>
       </c>
@@ -2411,7 +2420,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>292</v>
       </c>
@@ -2422,7 +2431,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>293</v>
       </c>
@@ -2433,7 +2442,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>294</v>
       </c>
@@ -2444,7 +2453,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>295</v>
       </c>
@@ -2455,7 +2464,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>296</v>
       </c>
@@ -2466,7 +2475,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>297</v>
       </c>
@@ -2477,7 +2486,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>298</v>
       </c>
@@ -2488,7 +2497,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>299</v>
       </c>
@@ -2499,7 +2508,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>300</v>
       </c>
@@ -2510,7 +2519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>301</v>
       </c>
@@ -2521,7 +2530,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>302</v>
       </c>
@@ -2532,7 +2541,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>303</v>
       </c>
@@ -2543,7 +2552,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>304</v>
       </c>
@@ -2554,7 +2563,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>305</v>
       </c>
@@ -2565,7 +2574,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>306</v>
       </c>
@@ -2576,7 +2585,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>307</v>
       </c>
@@ -2598,9 +2607,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>277</v>
       </c>
@@ -2611,7 +2620,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>280</v>
       </c>
@@ -2622,7 +2631,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>281</v>
       </c>
@@ -2633,7 +2642,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>282</v>
       </c>
@@ -2644,7 +2653,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>283</v>
       </c>
@@ -2655,7 +2664,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>284</v>
       </c>
@@ -2666,7 +2675,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>285</v>
       </c>
@@ -2677,7 +2686,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>286</v>
       </c>
@@ -2688,7 +2697,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>287</v>
       </c>
@@ -2699,7 +2708,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>288</v>
       </c>
@@ -2710,7 +2719,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>289</v>
       </c>
@@ -2721,7 +2730,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>290</v>
       </c>
@@ -2732,7 +2741,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>291</v>
       </c>
@@ -2743,7 +2752,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>292</v>
       </c>
@@ -2754,7 +2763,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>293</v>
       </c>
@@ -2765,7 +2774,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>294</v>
       </c>
@@ -2776,7 +2785,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>295</v>
       </c>
@@ -2787,7 +2796,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>296</v>
       </c>
@@ -2798,7 +2807,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>297</v>
       </c>
@@ -2809,7 +2818,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>298</v>
       </c>
@@ -2820,7 +2829,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>299</v>
       </c>
@@ -2831,7 +2840,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>300</v>
       </c>
@@ -2842,7 +2851,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>301</v>
       </c>
@@ -2853,7 +2862,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>302</v>
       </c>
@@ -2864,7 +2873,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>303</v>
       </c>
@@ -2875,7 +2884,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>304</v>
       </c>
@@ -2886,7 +2895,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>305</v>
       </c>
@@ -2897,7 +2906,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>306</v>
       </c>
@@ -2908,7 +2917,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>307</v>
       </c>
@@ -2930,9 +2939,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>277</v>
       </c>
@@ -2966,9 +2975,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CQ2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:95" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3255,7 +3264,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:95" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9850</v>
       </c>
@@ -3532,9 +3541,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -3587,7 +3596,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9850</v>
       </c>
@@ -3616,7 +3625,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9850</v>
       </c>
@@ -3651,7 +3660,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9850</v>
       </c>
@@ -3680,7 +3689,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9850</v>
       </c>
@@ -3730,7 +3739,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9850</v>
       </c>
@@ -3780,7 +3789,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9850</v>
       </c>
@@ -3815,7 +3824,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9850</v>
       </c>
@@ -3862,7 +3871,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9850</v>
       </c>
@@ -3891,7 +3900,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9850</v>
       </c>
@@ -3926,7 +3935,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9850</v>
       </c>
@@ -3961,7 +3970,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9850</v>
       </c>
@@ -4007,9 +4016,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -4041,7 +4050,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9850</v>
       </c>
@@ -4073,7 +4082,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9850</v>
       </c>
@@ -4105,7 +4114,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9850</v>
       </c>
@@ -4148,7 +4157,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -4160,9 +4169,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -4194,7 +4203,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9850</v>
       </c>
@@ -4237,9 +4246,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -4256,7 +4265,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9850</v>
       </c>
@@ -4278,7 +4287,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -4290,9 +4299,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -4342,7 +4351,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9850</v>
       </c>
@@ -4392,7 +4401,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9850</v>
       </c>
@@ -4442,7 +4451,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9850</v>
       </c>
@@ -4492,7 +4501,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9850</v>
       </c>
@@ -4542,7 +4551,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9850</v>
       </c>
@@ -4592,7 +4601,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9850</v>
       </c>
@@ -4642,7 +4651,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9850</v>
       </c>
@@ -4692,7 +4701,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9850</v>
       </c>
@@ -4742,7 +4751,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9850</v>
       </c>
@@ -4792,7 +4801,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9850</v>
       </c>
@@ -4842,7 +4851,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9850</v>
       </c>
@@ -4892,7 +4901,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9850</v>
       </c>
@@ -4942,7 +4951,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9850</v>
       </c>
@@ -4992,7 +5001,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9850</v>
       </c>
@@ -5042,7 +5051,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9850</v>
       </c>
@@ -5092,7 +5101,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9850</v>
       </c>
@@ -5142,7 +5151,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9850</v>
       </c>
@@ -5192,7 +5201,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9850</v>
       </c>
@@ -5242,7 +5251,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9850</v>
       </c>
@@ -5292,7 +5301,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9850</v>
       </c>
@@ -5342,7 +5351,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9850</v>
       </c>
@@ -5392,7 +5401,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9850</v>
       </c>
@@ -5442,7 +5451,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9850</v>
       </c>
@@ -5492,7 +5501,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9850</v>
       </c>
@@ -5542,7 +5551,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9850</v>
       </c>
@@ -5592,7 +5601,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9850</v>
       </c>
@@ -5621,7 +5630,7 @@
         <v>236</v>
       </c>
       <c r="J27" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="K27" t="s">
         <v>238</v>
@@ -5642,7 +5651,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9850</v>
       </c>
@@ -5671,7 +5680,7 @@
         <v>236</v>
       </c>
       <c r="J28" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="K28" t="s">
         <v>252</v>
@@ -5692,7 +5701,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9850</v>
       </c>
@@ -5721,7 +5730,7 @@
         <v>236</v>
       </c>
       <c r="J29" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="K29" t="s">
         <v>254</v>
@@ -5729,7 +5738,7 @@
       <c r="L29" t="s">
         <v>254</v>
       </c>
-      <c r="M29" t="s">
+      <c r="M29" s="2" t="s">
         <v>227</v>
       </c>
       <c r="N29" t="s">
@@ -5742,7 +5751,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9850</v>
       </c>
@@ -5771,7 +5780,7 @@
         <v>236</v>
       </c>
       <c r="J30" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="K30" t="s">
         <v>248</v>
@@ -5792,7 +5801,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9850</v>
       </c>
@@ -5821,7 +5830,7 @@
         <v>236</v>
       </c>
       <c r="J31" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="K31" t="s">
         <v>257</v>
@@ -5842,7 +5851,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9850</v>
       </c>
@@ -5871,7 +5880,7 @@
         <v>236</v>
       </c>
       <c r="J32" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="K32" t="s">
         <v>268</v>
@@ -5892,7 +5901,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9850</v>
       </c>
@@ -5921,7 +5930,7 @@
         <v>236</v>
       </c>
       <c r="J33" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="K33" t="s">
         <v>259</v>
@@ -5942,7 +5951,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9850</v>
       </c>
@@ -5971,7 +5980,7 @@
         <v>236</v>
       </c>
       <c r="J34" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="K34" t="s">
         <v>232</v>
@@ -5992,7 +6001,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9850</v>
       </c>
@@ -6021,7 +6030,7 @@
         <v>236</v>
       </c>
       <c r="J35" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="K35" t="s">
         <v>243</v>
@@ -6042,7 +6051,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9850</v>
       </c>
@@ -6071,7 +6080,7 @@
         <v>236</v>
       </c>
       <c r="J36" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="K36" t="s">
         <v>245</v>
@@ -6095,7 +6104,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P8 A16:P36 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:P8 A16:P26 A9:D9 F9:P9 A10:D15 F10:P15 A27:I36 K27:P36" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>